--- a/floristics_data/waypoints/waypoint_data.xlsx
+++ b/floristics_data/waypoints/waypoint_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gwenr\Documents\Git\junction_floristics\floristics_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gwenr\Documents\Git\junction_floristics\floristics_data\waypoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{41CF6EE0-2D19-44B3-B3CC-129262CEA1D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA484CF-9E50-4340-B1E8-5F1ACE7235F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{03D364FD-000D-4535-8B16-609126CB0F92}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="221">
   <si>
     <t>name</t>
   </si>
@@ -80,18 +80,12 @@
     <t>Very grassy, roughly 15 ft high canopy composed of juniper, mesquite, and texas persimmon. On the Agarita trail.</t>
   </si>
   <si>
-    <t>ball</t>
-  </si>
-  <si>
     <t>TTU</t>
   </si>
   <si>
     <t>journal7</t>
   </si>
   <si>
-    <t>Along paved trail at TTUJ river access point. Grass, brambles, in open.</t>
-  </si>
-  <si>
     <t>berberis</t>
   </si>
   <si>
@@ -125,12 +119,6 @@
     <t>Somewhat shaded, roughly 100 ft canopy of pecan, mesquite understory, very lush.</t>
   </si>
   <si>
-    <t>buffalo2</t>
-  </si>
-  <si>
-    <t>Next to trail, roughly 70 ft pecan canopy, lots of grass, near buck lake.</t>
-  </si>
-  <si>
     <t>bur</t>
   </si>
   <si>
@@ -212,12 +200,6 @@
     <t>false_olive</t>
   </si>
   <si>
-    <t>ferncactus</t>
-  </si>
-  <si>
-    <t>Limestone rocks, juniper and Rhus virens.</t>
-  </si>
-  <si>
     <t>feverfew</t>
   </si>
   <si>
@@ -230,12 +212,6 @@
     <t>On rocky slope, moss and lichen, lots of juniper and oak, many dead.</t>
   </si>
   <si>
-    <t>glory</t>
-  </si>
-  <si>
-    <t>Along trail, in open. Opuntia, grass, cedar elm, verbenas, thistles.</t>
-  </si>
-  <si>
     <t>grass</t>
   </si>
   <si>
@@ -266,18 +242,6 @@
     <t>Along dirt road used by park near turkey roost area, right off paved road. Very grassy, lots of oaks.</t>
   </si>
   <si>
-    <t>headchog</t>
-  </si>
-  <si>
-    <t>Very rocky ground, Rhus virens, Opuntia, lots of grass including B. curtipendula. Open, right off Walter's way.</t>
-  </si>
-  <si>
-    <t>horse</t>
-  </si>
-  <si>
-    <t>Along bank of South Llano River in the wash, short willow very common, no tree cover.</t>
-  </si>
-  <si>
     <t>hotpink</t>
   </si>
   <si>
@@ -293,12 +257,6 @@
     <t>Right by the gate that opens onto midcanyon trail. Open grassy area ringed by thicker vegetation, including juniper.</t>
   </si>
   <si>
-    <t>lily</t>
-  </si>
-  <si>
-    <t>Near bridge at park entrance.</t>
-  </si>
-  <si>
     <t>liverwort</t>
   </si>
   <si>
@@ -356,24 +314,6 @@
     <t>On side of road outside river trail parking.</t>
   </si>
   <si>
-    <t>nipple</t>
-  </si>
-  <si>
-    <t>On side of service road that connects to Fawn trail. Shaded.</t>
-  </si>
-  <si>
-    <t>oats</t>
-  </si>
-  <si>
-    <t>Near river, very shaded by pecans roughly 50 ft tall. Lots of grass and frostweed.</t>
-  </si>
-  <si>
-    <t>orangethroat</t>
-  </si>
-  <si>
-    <t>Along trail, in open. Lots of horehound.</t>
-  </si>
-  <si>
     <t>pecan</t>
   </si>
   <si>
@@ -401,42 +341,12 @@
     <t>Description was added after the fact. 5/20/2025  11:36:46 AM</t>
   </si>
   <si>
-    <t>prim</t>
-  </si>
-  <si>
-    <t>At TTUJ old kayak launch point. Next to road/bridge. Pool of the South Llano River, destabilized bank, big rocks, open.</t>
-  </si>
-  <si>
-    <t>realfern</t>
-  </si>
-  <si>
-    <t>On rocky slope with juniper, oak, sotol, Rhus virens, Opuntia.</t>
-  </si>
-  <si>
-    <t>realfern2</t>
-  </si>
-  <si>
-    <t>Rocky ledge under juniper.</t>
-  </si>
-  <si>
     <t>red</t>
   </si>
   <si>
     <t>Fairly open, ephedra and cacti nearby. Juniper canopy farther out. Flat.</t>
   </si>
   <si>
-    <t>redsage</t>
-  </si>
-  <si>
-    <t>In Fawn trail, rocky wash area. Lots of juniper, Schyziarum scoparium.</t>
-  </si>
-  <si>
-    <t>reticulata</t>
-  </si>
-  <si>
-    <t>Along roadside next to park headquarters, oak and juniper cover.</t>
-  </si>
-  <si>
     <t>river_relax</t>
   </si>
   <si>
@@ -473,18 +383,6 @@
     <t>Still area along edge of South Llano River.</t>
   </si>
   <si>
-    <t>spiderfern</t>
-  </si>
-  <si>
-    <t>In shaded corner of river, water much colder than main river (possibly a spring).</t>
-  </si>
-  <si>
-    <t>sting</t>
-  </si>
-  <si>
-    <t>Shaded by roughly 70 ft pecan canopy, lush, lots of grass and asters (frostweed).</t>
-  </si>
-  <si>
     <t>skeleton</t>
   </si>
   <si>
@@ -762,12 +660,6 @@
   </si>
   <si>
     <t>On rocky hill top, lots of grass (including Bouteloua), very open, scattered juniper, oak, and agarita</t>
-  </si>
-  <si>
-    <t>warnock</t>
-  </si>
-  <si>
-    <t>Oak, Rhus virens, juniper, lots of grass, Opuntia. Elevated, open, rocky.</t>
   </si>
   <si>
     <t>warty</t>
@@ -1148,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90F86194-E18A-4F17-84C6-B31C9EA1B7C9}">
-  <dimension ref="A1:I115"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="15.5234375" customWidth="1"/>
@@ -1198,10 +1090,10 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D2" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E2">
         <v>540.1</v>
@@ -1216,91 +1108,94 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
       <c r="C3">
-        <v>30.470153</v>
+        <v>30.479230000000001</v>
       </c>
       <c r="D3">
-        <v>-99.784595999999993</v>
+        <v>-99.800780000000003</v>
       </c>
       <c r="E3">
-        <v>516</v>
+        <v>593.4</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4">
-        <v>30.479230000000001</v>
-      </c>
-      <c r="D4">
-        <v>-99.800780000000003</v>
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D4" t="s">
+        <v>220</v>
       </c>
       <c r="E4">
-        <v>593.4</v>
+        <v>540.1</v>
       </c>
       <c r="F4">
         <v>50</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>21</v>
+      </c>
+      <c r="I4" s="3">
+        <v>45797.398553240739</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D5" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E5">
-        <v>540.1</v>
+        <v>524</v>
       </c>
       <c r="F5">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="3">
-        <v>45797.398553240739</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="I5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1308,25 +1203,22 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D6" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E6">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="I6" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -1337,13 +1229,13 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D7" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E7">
-        <v>523</v>
+        <v>533.4</v>
       </c>
       <c r="F7">
         <v>15</v>
@@ -1354,8 +1246,11 @@
       <c r="H7" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1363,80 +1258,80 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D8" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E8">
-        <v>524</v>
+        <v>528.79999999999995</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="I8" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" t="s">
-        <v>256</v>
-      </c>
-      <c r="D9" t="s">
-        <v>256</v>
+        <v>13</v>
+      </c>
+      <c r="C9">
+        <v>30.478929999999998</v>
+      </c>
+      <c r="D9">
+        <v>-99.801050000000004</v>
       </c>
       <c r="E9">
-        <v>533.4</v>
+        <v>601.70000000000005</v>
       </c>
       <c r="F9">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D10" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E10">
-        <v>528.79999999999995</v>
+        <v>529.1</v>
       </c>
       <c r="F10">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I10" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -1444,115 +1339,112 @@
         <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11">
-        <v>30.478929999999998</v>
-      </c>
-      <c r="D11">
-        <v>-99.801050000000004</v>
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>220</v>
+      </c>
+      <c r="D11" t="s">
+        <v>220</v>
       </c>
       <c r="E11">
-        <v>601.70000000000005</v>
+        <v>534.9</v>
       </c>
       <c r="F11">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="I11" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D12" t="s">
-        <v>256</v>
+        <v>13</v>
+      </c>
+      <c r="C12">
+        <v>30.475739999999998</v>
+      </c>
+      <c r="D12">
+        <v>-99.797190000000001</v>
       </c>
       <c r="E12">
-        <v>529.1</v>
+        <v>541.29999999999995</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I12" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D13" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E13">
-        <v>534.9</v>
+        <v>545.9</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14">
-        <v>30.475739999999998</v>
-      </c>
-      <c r="D14">
-        <v>-99.797190000000001</v>
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>220</v>
+      </c>
+      <c r="D14" t="s">
+        <v>220</v>
       </c>
       <c r="E14">
-        <v>541.29999999999995</v>
+        <v>565.70000000000005</v>
       </c>
       <c r="F14">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I14" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>46</v>
       </c>
@@ -1560,16 +1452,16 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D15" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E15">
-        <v>545.9</v>
+        <v>534.9</v>
       </c>
       <c r="F15">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>11</v>
@@ -1577,63 +1469,69 @@
       <c r="H15" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="I15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D16" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E16">
-        <v>565.70000000000005</v>
+        <v>559.9</v>
       </c>
       <c r="F16">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+        <v>51</v>
+      </c>
+      <c r="I16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D17" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E17">
-        <v>534.9</v>
+        <v>573.9</v>
       </c>
       <c r="F17">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>51</v>
       </c>
       <c r="I17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -1641,57 +1539,54 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D18" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E18">
-        <v>559.9</v>
+        <v>611.70000000000005</v>
       </c>
       <c r="F18">
         <v>10</v>
       </c>
       <c r="G18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I18" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" t="s">
+        <v>220</v>
+      </c>
+      <c r="D19" t="s">
+        <v>220</v>
+      </c>
+      <c r="E19">
+        <v>591</v>
+      </c>
+      <c r="F19">
+        <v>50</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" t="s">
-        <v>256</v>
-      </c>
-      <c r="D19" t="s">
-        <v>256</v>
-      </c>
-      <c r="E19">
-        <v>573.9</v>
-      </c>
-      <c r="F19">
-        <v>10</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="I19" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>57</v>
       </c>
@@ -1699,204 +1594,210 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D20" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E20">
-        <v>605.9</v>
+        <v>556.9</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="H20" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" t="s">
-        <v>59</v>
-      </c>
       <c r="B21" t="s">
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D21" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E21">
-        <v>611.70000000000005</v>
+        <v>529.1</v>
       </c>
       <c r="F21">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D22" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E22">
-        <v>591</v>
+        <v>530</v>
       </c>
       <c r="F22">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="I22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B23" t="s">
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D23" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E23">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="F23">
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
+      </c>
+      <c r="I23" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B24" t="s">
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D24" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E24">
-        <v>556.9</v>
+        <v>527.29999999999995</v>
       </c>
       <c r="F24">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="I24" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D25" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E25">
-        <v>529.1</v>
+        <v>533.1</v>
       </c>
       <c r="F25">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" t="s">
-        <v>68</v>
-      </c>
       <c r="B26" t="s">
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D26" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E26">
-        <v>530</v>
+        <v>605</v>
       </c>
       <c r="F26">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D27" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E27">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="F27">
         <v>10</v>
@@ -1905,1197 +1806,1230 @@
         <v>11</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I27" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" t="s">
+        <v>220</v>
+      </c>
+      <c r="D28" t="s">
+        <v>220</v>
+      </c>
+      <c r="E28">
+        <v>542.79999999999995</v>
+      </c>
+      <c r="F28">
+        <v>10</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" t="s">
-        <v>256</v>
-      </c>
-      <c r="D28" t="s">
-        <v>256</v>
-      </c>
-      <c r="E28">
-        <v>527.29999999999995</v>
-      </c>
-      <c r="F28">
-        <v>10</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H28" s="2" t="s">
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
         <v>72</v>
       </c>
-      <c r="I28" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" t="s">
+        <v>220</v>
+      </c>
+      <c r="D29" t="s">
+        <v>220</v>
+      </c>
+      <c r="E29">
+        <v>522.1</v>
+      </c>
+      <c r="F29">
+        <v>10</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B29" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" t="s">
-        <v>256</v>
-      </c>
-      <c r="D29" t="s">
-        <v>256</v>
-      </c>
-      <c r="E29">
-        <v>533.1</v>
-      </c>
-      <c r="F29">
-        <v>10</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="I29" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" t="s">
+        <v>220</v>
+      </c>
+      <c r="D30" t="s">
+        <v>220</v>
+      </c>
+      <c r="E30">
+        <v>560.20000000000005</v>
+      </c>
+      <c r="F30">
+        <v>110</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" t="s">
-        <v>256</v>
-      </c>
-      <c r="D30" t="s">
-        <v>256</v>
-      </c>
-      <c r="E30">
-        <v>612</v>
-      </c>
-      <c r="F30">
-        <v>10</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H30" s="2" t="s">
+      <c r="I30" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>77</v>
       </c>
       <c r="B31" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31">
-        <v>30.470113999999999</v>
-      </c>
-      <c r="D31">
-        <v>-99.785120000000006</v>
+        <v>10</v>
+      </c>
+      <c r="C31" t="s">
+        <v>220</v>
+      </c>
+      <c r="D31" t="s">
+        <v>220</v>
       </c>
       <c r="E31">
-        <v>516</v>
+        <v>557.5</v>
       </c>
       <c r="F31">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="I31" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D32" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E32">
-        <v>605</v>
+        <v>541.9</v>
       </c>
       <c r="F32">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D33" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E33">
-        <v>523</v>
+        <v>555</v>
       </c>
       <c r="F33">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>83</v>
+      </c>
+      <c r="I33" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D34" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E34">
-        <v>542.79999999999995</v>
+        <v>531</v>
       </c>
       <c r="F34">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
       </c>
       <c r="C35" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D35" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E35">
-        <v>524</v>
+        <v>534.9</v>
       </c>
       <c r="F35">
         <v>10</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
+      </c>
+      <c r="I35" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
       </c>
       <c r="C36" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D36" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E36">
-        <v>522.1</v>
+        <v>526.1</v>
       </c>
       <c r="F36">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I36" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" t="s">
-        <v>256</v>
-      </c>
-      <c r="D37" t="s">
-        <v>256</v>
+        <v>13</v>
+      </c>
+      <c r="C37">
+        <v>30.478338999999998</v>
+      </c>
+      <c r="D37">
+        <v>-99.778989999999993</v>
       </c>
       <c r="E37">
-        <v>560.20000000000005</v>
+        <v>515.4</v>
       </c>
       <c r="F37">
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I37" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B38" t="s">
         <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D38" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E38">
-        <v>557.5</v>
+        <v>531.29999999999995</v>
       </c>
       <c r="F38">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I38" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B39" t="s">
         <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D39" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E39">
-        <v>541.9</v>
+        <v>525.20000000000005</v>
       </c>
       <c r="F39">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B40" t="s">
         <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D40" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E40">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="F40">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B41" t="s">
         <v>10</v>
       </c>
       <c r="C41" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D41" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E41">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="F41">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
+      </c>
+      <c r="I41" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B42" t="s">
         <v>10</v>
       </c>
       <c r="C42" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D42" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E42">
-        <v>534.9</v>
+        <v>526.1</v>
       </c>
       <c r="F42">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I42" t="s">
-        <v>20</v>
+        <v>106</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B43" t="s">
         <v>10</v>
       </c>
       <c r="C43" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D43" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E43">
-        <v>526.1</v>
+        <v>524.9</v>
       </c>
       <c r="F43">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B44" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" t="s">
-        <v>256</v>
-      </c>
-      <c r="D44" t="s">
-        <v>256</v>
+        <v>13</v>
+      </c>
+      <c r="C44">
+        <v>30.481106</v>
+      </c>
+      <c r="D44">
+        <v>-99.804687999999999</v>
       </c>
       <c r="E44">
-        <v>542.79999999999995</v>
+        <v>612</v>
       </c>
       <c r="F44">
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I44" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
+        <v>112</v>
+      </c>
+      <c r="B45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" t="s">
+        <v>220</v>
+      </c>
+      <c r="D45" t="s">
+        <v>220</v>
+      </c>
+      <c r="E45">
+        <v>524.9</v>
+      </c>
+      <c r="F45">
         <v>15</v>
       </c>
-      <c r="H44" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I44" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" t="s">
-        <v>107</v>
-      </c>
-      <c r="B45" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" t="s">
-        <v>256</v>
-      </c>
-      <c r="D45" t="s">
-        <v>256</v>
-      </c>
-      <c r="E45">
-        <v>523</v>
-      </c>
-      <c r="F45">
-        <v>10</v>
-      </c>
       <c r="G45" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+        <v>113</v>
+      </c>
+      <c r="I45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B46" t="s">
         <v>10</v>
       </c>
       <c r="C46" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D46" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E46">
-        <v>524.9</v>
+        <v>517.1</v>
       </c>
       <c r="F46">
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>96</v>
+      </c>
+      <c r="I46" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
-        <v>14</v>
-      </c>
-      <c r="C47">
-        <v>30.478338999999998</v>
-      </c>
-      <c r="D47">
-        <v>-99.778989999999993</v>
+        <v>10</v>
+      </c>
+      <c r="C47" t="s">
+        <v>220</v>
+      </c>
+      <c r="D47" t="s">
+        <v>220</v>
       </c>
       <c r="E47">
-        <v>515.4</v>
+        <v>566</v>
       </c>
       <c r="F47">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="I47" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B48" t="s">
         <v>10</v>
       </c>
       <c r="C48" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D48" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E48">
-        <v>531.29999999999995</v>
+        <v>566.9</v>
       </c>
       <c r="F48">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G48" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I48" t="s">
         <v>18</v>
       </c>
-      <c r="H48" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I48" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="49" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
+        <v>121</v>
+      </c>
+      <c r="B49" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" t="s">
+        <v>220</v>
+      </c>
+      <c r="D49" t="s">
+        <v>220</v>
+      </c>
+      <c r="E49">
+        <v>566.9</v>
+      </c>
+      <c r="F49">
+        <v>50</v>
+      </c>
+      <c r="G49" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B49" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" t="s">
-        <v>256</v>
-      </c>
-      <c r="D49" t="s">
-        <v>256</v>
-      </c>
-      <c r="E49">
-        <v>525.20000000000005</v>
-      </c>
-      <c r="F49">
-        <v>50</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="H49" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B50" t="s">
-        <v>14</v>
-      </c>
-      <c r="C50">
-        <v>30.478670000000001</v>
-      </c>
-      <c r="D50">
-        <v>-99.777826000000005</v>
+        <v>10</v>
+      </c>
+      <c r="C50" t="s">
+        <v>220</v>
+      </c>
+      <c r="D50" t="s">
+        <v>220</v>
       </c>
       <c r="E50">
-        <v>515.1</v>
+        <v>609</v>
       </c>
       <c r="F50">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I50" s="3"/>
+        <v>124</v>
+      </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B51" t="s">
         <v>10</v>
       </c>
       <c r="C51" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D51" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E51">
         <v>609</v>
       </c>
       <c r="F51">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="I51" s="3"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+        <v>126</v>
+      </c>
+      <c r="I51" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B52" t="s">
         <v>10</v>
       </c>
       <c r="C52" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D52" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E52">
-        <v>608</v>
+        <v>604.70000000000005</v>
       </c>
       <c r="F52">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I52" s="3"/>
+        <v>126</v>
+      </c>
+      <c r="I52" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="53" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D53" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E53">
-        <v>545</v>
+        <v>611.1</v>
       </c>
       <c r="F53">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I53" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" t="s">
+        <v>136</v>
+      </c>
+      <c r="B54" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" t="s">
+        <v>220</v>
+      </c>
+      <c r="D54" t="s">
+        <v>220</v>
+      </c>
+      <c r="E54">
+        <v>524.9</v>
+      </c>
+      <c r="F54">
+        <v>50</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I54" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" t="s">
+        <v>133</v>
+      </c>
+      <c r="B55" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" t="s">
+        <v>220</v>
+      </c>
+      <c r="D55" t="s">
+        <v>220</v>
+      </c>
+      <c r="E55">
+        <v>524.9</v>
+      </c>
+      <c r="F55">
+        <v>50</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I55" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" t="s">
+        <v>137</v>
+      </c>
+      <c r="B56" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s">
+        <v>220</v>
+      </c>
+      <c r="D56" t="s">
+        <v>220</v>
+      </c>
+      <c r="E56">
+        <v>526.9</v>
+      </c>
+      <c r="F56">
+        <v>50</v>
+      </c>
+      <c r="G56" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" t="s">
-        <v>128</v>
-      </c>
-      <c r="B54" t="s">
-        <v>10</v>
-      </c>
-      <c r="C54" t="s">
-        <v>256</v>
-      </c>
-      <c r="D54" t="s">
-        <v>256</v>
-      </c>
-      <c r="E54">
-        <v>570.9</v>
-      </c>
-      <c r="F54">
-        <v>10</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" t="s">
-        <v>130</v>
-      </c>
-      <c r="B55" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" t="s">
-        <v>256</v>
-      </c>
-      <c r="D55" t="s">
-        <v>256</v>
-      </c>
-      <c r="E55">
-        <v>537</v>
-      </c>
-      <c r="F55">
-        <v>10</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" t="s">
-        <v>132</v>
-      </c>
-      <c r="B56" t="s">
-        <v>10</v>
-      </c>
-      <c r="C56" t="s">
-        <v>256</v>
-      </c>
-      <c r="D56" t="s">
-        <v>256</v>
-      </c>
-      <c r="E56">
-        <v>524</v>
-      </c>
-      <c r="F56">
-        <v>100</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="H56" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="I56" t="s">
-        <v>134</v>
+        <v>138</v>
+      </c>
+      <c r="I56" s="3">
+        <v>45797.418333333335</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B57" t="s">
         <v>10</v>
       </c>
       <c r="C57" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D57" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E57">
-        <v>526.1</v>
+        <v>530.29999999999995</v>
       </c>
       <c r="F57">
         <v>50</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+        <v>140</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
       </c>
       <c r="C58" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D58" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E58">
-        <v>524.9</v>
+        <v>528.6</v>
       </c>
       <c r="F58">
         <v>50</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+        <v>140</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B59" t="s">
-        <v>14</v>
-      </c>
-      <c r="C59">
-        <v>30.481106</v>
-      </c>
-      <c r="D59">
-        <v>-99.804687999999999</v>
+        <v>10</v>
+      </c>
+      <c r="C59" t="s">
+        <v>220</v>
+      </c>
+      <c r="D59" t="s">
+        <v>220</v>
       </c>
       <c r="E59">
-        <v>612</v>
+        <v>525.20000000000005</v>
       </c>
       <c r="F59">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I59" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+        <v>145</v>
+      </c>
+      <c r="I59" s="3">
+        <v>45797.486458333333</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B60" t="s">
         <v>10</v>
       </c>
       <c r="C60" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D60" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E60">
-        <v>524.9</v>
+        <v>588.9</v>
       </c>
       <c r="F60">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I60" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" t="s">
+        <v>146</v>
+      </c>
+      <c r="B61" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" t="s">
+        <v>220</v>
+      </c>
+      <c r="D61" t="s">
+        <v>220</v>
+      </c>
+      <c r="E61">
+        <v>588</v>
+      </c>
+      <c r="F61" t="s">
+        <v>147</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I61" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" t="s">
+        <v>153</v>
+      </c>
+      <c r="B62" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" t="s">
+        <v>220</v>
+      </c>
+      <c r="D62" t="s">
+        <v>220</v>
+      </c>
+      <c r="E62">
+        <v>590.1</v>
+      </c>
+      <c r="F62">
+        <v>50</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I62" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" t="s">
+        <v>150</v>
+      </c>
+      <c r="B63" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" t="s">
+        <v>220</v>
+      </c>
+      <c r="D63" t="s">
+        <v>220</v>
+      </c>
+      <c r="E63">
+        <v>588.9</v>
+      </c>
+      <c r="F63" t="s">
+        <v>147</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I63" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" t="s">
+        <v>158</v>
+      </c>
+      <c r="B64" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" t="s">
+        <v>220</v>
+      </c>
+      <c r="D64" t="s">
+        <v>220</v>
+      </c>
+      <c r="E64">
+        <v>532.20000000000005</v>
+      </c>
+      <c r="F64">
+        <v>50</v>
+      </c>
+      <c r="G64" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" t="s">
-        <v>144</v>
-      </c>
-      <c r="B61" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" t="s">
-        <v>256</v>
-      </c>
-      <c r="D61" t="s">
-        <v>256</v>
-      </c>
-      <c r="E61">
-        <v>526</v>
-      </c>
-      <c r="F61">
-        <v>10</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" t="s">
-        <v>146</v>
-      </c>
-      <c r="B62" t="s">
-        <v>10</v>
-      </c>
-      <c r="C62" t="s">
-        <v>256</v>
-      </c>
-      <c r="D62" t="s">
-        <v>256</v>
-      </c>
-      <c r="E62">
-        <v>524</v>
-      </c>
-      <c r="F62">
-        <v>10</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" t="s">
-        <v>148</v>
-      </c>
-      <c r="B63" t="s">
-        <v>10</v>
-      </c>
-      <c r="C63" t="s">
-        <v>256</v>
-      </c>
-      <c r="D63" t="s">
-        <v>256</v>
-      </c>
-      <c r="E63">
-        <v>517.1</v>
-      </c>
-      <c r="F63">
-        <v>10</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I63" t="s">
+      <c r="H64" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" t="s">
+        <v>155</v>
+      </c>
+      <c r="B65" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" t="s">
+        <v>220</v>
+      </c>
+      <c r="D65" t="s">
+        <v>220</v>
+      </c>
+      <c r="E65">
+        <v>530</v>
+      </c>
+      <c r="F65">
+        <v>27</v>
+      </c>
+      <c r="G65" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" t="s">
-        <v>150</v>
-      </c>
-      <c r="B64" t="s">
-        <v>10</v>
-      </c>
-      <c r="C64" t="s">
-        <v>256</v>
-      </c>
-      <c r="D64" t="s">
-        <v>256</v>
-      </c>
-      <c r="E64">
-        <v>566.9</v>
-      </c>
-      <c r="F64">
-        <v>50</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I64" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" t="s">
-        <v>153</v>
-      </c>
-      <c r="B65" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" t="s">
-        <v>256</v>
-      </c>
-      <c r="D65" t="s">
-        <v>256</v>
-      </c>
-      <c r="E65">
-        <v>566</v>
-      </c>
-      <c r="F65">
-        <v>50</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>151</v>
-      </c>
       <c r="H65" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I65" t="s">
-        <v>20</v>
+        <v>156</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B66" t="s">
         <v>10</v>
       </c>
       <c r="C66" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D66" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E66">
-        <v>566.9</v>
+        <v>532.20000000000005</v>
       </c>
       <c r="F66">
         <v>50</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+        <v>161</v>
+      </c>
+      <c r="I66" s="3">
+        <v>45797.598749999997</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B67" t="s">
         <v>10</v>
       </c>
       <c r="C67" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D67" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E67">
-        <v>609</v>
+        <v>588.6</v>
       </c>
       <c r="F67">
         <v>50</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+        <v>163</v>
+      </c>
+      <c r="I67" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B68" t="s">
         <v>10</v>
       </c>
       <c r="C68" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D68" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E68">
-        <v>609</v>
+        <v>592.5</v>
       </c>
       <c r="F68">
         <v>50</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I68" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B69" t="s">
         <v>10</v>
       </c>
       <c r="C69" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D69" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E69">
-        <v>611.1</v>
+        <v>584.9</v>
       </c>
       <c r="F69">
         <v>50</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>54</v>
+        <v>166</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="I69" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="70" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B70" t="s">
         <v>10</v>
       </c>
       <c r="C70" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D70" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E70">
-        <v>604.70000000000005</v>
+        <v>611.1</v>
       </c>
       <c r="F70">
         <v>50</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>166</v>
+        <v>117</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="I70" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>167</v>
       </c>
@@ -3103,28 +3037,25 @@
         <v>10</v>
       </c>
       <c r="C71" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D71" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E71">
-        <v>524.9</v>
+        <v>612</v>
       </c>
       <c r="F71">
         <v>50</v>
       </c>
       <c r="G71" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H71" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="H71" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I71" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="72" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>170</v>
       </c>
@@ -3132,25 +3063,22 @@
         <v>10</v>
       </c>
       <c r="C72" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D72" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E72">
-        <v>524.9</v>
+        <v>609.9</v>
       </c>
       <c r="F72">
         <v>50</v>
       </c>
       <c r="G72" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H72" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I72" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3161,425 +3089,419 @@
         <v>10</v>
       </c>
       <c r="C73" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D73" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E73">
-        <v>526.9</v>
+        <v>523</v>
       </c>
       <c r="F73">
         <v>50</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H73" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" t="s">
         <v>172</v>
       </c>
-      <c r="I73" s="3">
-        <v>45797.418333333335</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" t="s">
+      <c r="B74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C74" t="s">
+        <v>220</v>
+      </c>
+      <c r="D74" t="s">
+        <v>220</v>
+      </c>
+      <c r="E74">
+        <v>540.1</v>
+      </c>
+      <c r="F74">
+        <v>332</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H74" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B74" t="s">
-        <v>10</v>
-      </c>
-      <c r="C74" t="s">
-        <v>256</v>
-      </c>
-      <c r="D74" t="s">
-        <v>256</v>
-      </c>
-      <c r="E74">
-        <v>528.6</v>
-      </c>
-      <c r="F74">
-        <v>50</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H74" s="2" t="s">
+      <c r="I74" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" t="s">
         <v>174</v>
       </c>
-      <c r="I74" s="3" t="s">
+      <c r="B75" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" t="s">
+        <v>220</v>
+      </c>
+      <c r="D75" t="s">
+        <v>220</v>
+      </c>
+      <c r="E75">
+        <v>534.9</v>
+      </c>
+      <c r="F75">
+        <v>10</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H75" s="2" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="75" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" t="s">
+      <c r="I75" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" t="s">
         <v>176</v>
       </c>
-      <c r="B75" t="s">
-        <v>10</v>
-      </c>
-      <c r="C75" t="s">
-        <v>256</v>
-      </c>
-      <c r="D75" t="s">
-        <v>256</v>
-      </c>
-      <c r="E75">
-        <v>530.29999999999995</v>
-      </c>
-      <c r="F75">
-        <v>50</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I75" s="3" t="s">
+      <c r="B76" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" t="s">
+        <v>220</v>
+      </c>
+      <c r="D76" t="s">
+        <v>220</v>
+      </c>
+      <c r="E76">
+        <v>522.1</v>
+      </c>
+      <c r="F76">
+        <v>15</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H76" s="2" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" t="s">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" t="s">
         <v>178</v>
       </c>
-      <c r="B76" t="s">
-        <v>10</v>
-      </c>
-      <c r="C76" t="s">
-        <v>256</v>
-      </c>
-      <c r="D76" t="s">
-        <v>256</v>
-      </c>
-      <c r="E76">
-        <v>525.20000000000005</v>
-      </c>
-      <c r="F76">
-        <v>95</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H76" s="2" t="s">
+      <c r="B77" t="s">
+        <v>13</v>
+      </c>
+      <c r="C77">
+        <v>30.481009</v>
+      </c>
+      <c r="D77">
+        <v>-99.803982000000005</v>
+      </c>
+      <c r="E77">
+        <v>608.1</v>
+      </c>
+      <c r="F77">
+        <v>10</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" t="s">
         <v>179</v>
       </c>
-      <c r="I76" s="3">
-        <v>45797.486458333333</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ht="57.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" t="s">
+      <c r="B78" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" t="s">
+        <v>220</v>
+      </c>
+      <c r="D78" t="s">
+        <v>220</v>
+      </c>
+      <c r="E78">
+        <v>592.5</v>
+      </c>
+      <c r="F78">
+        <v>60</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H78" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B77" t="s">
-        <v>10</v>
-      </c>
-      <c r="C77" t="s">
-        <v>256</v>
-      </c>
-      <c r="D77" t="s">
-        <v>256</v>
-      </c>
-      <c r="E77">
-        <v>588</v>
-      </c>
-      <c r="F77" t="s">
-        <v>181</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="I77" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="57.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" t="s">
-        <v>183</v>
-      </c>
-      <c r="B78" t="s">
-        <v>10</v>
-      </c>
-      <c r="C78" t="s">
-        <v>256</v>
-      </c>
-      <c r="D78" t="s">
-        <v>256</v>
-      </c>
-      <c r="E78">
-        <v>588.9</v>
-      </c>
-      <c r="F78">
-        <v>50</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="I78" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="79" spans="1:9" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>184</v>
       </c>
       <c r="B79" t="s">
-        <v>10</v>
-      </c>
-      <c r="C79" t="s">
-        <v>256</v>
-      </c>
-      <c r="D79" t="s">
-        <v>256</v>
+        <v>13</v>
+      </c>
+      <c r="C79">
+        <v>30.476849999999999</v>
+      </c>
+      <c r="D79">
+        <v>-99.799880000000002</v>
       </c>
       <c r="E79">
-        <v>588.9</v>
-      </c>
-      <c r="F79" t="s">
-        <v>181</v>
+        <v>580.29999999999995</v>
+      </c>
+      <c r="F79">
+        <v>50</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>185</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I79" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:9" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
+        <v>181</v>
+      </c>
+      <c r="B80" t="s">
+        <v>13</v>
+      </c>
+      <c r="C80">
+        <v>30.476970000000001</v>
+      </c>
+      <c r="D80">
+        <v>-99.799980000000005</v>
+      </c>
+      <c r="E80">
+        <v>583.70000000000005</v>
+      </c>
+      <c r="F80">
+        <v>50</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I80" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" t="s">
         <v>187</v>
       </c>
-      <c r="B80" t="s">
-        <v>10</v>
-      </c>
-      <c r="C80" t="s">
-        <v>256</v>
-      </c>
-      <c r="D80" t="s">
-        <v>256</v>
-      </c>
-      <c r="E80">
-        <v>590.1</v>
-      </c>
-      <c r="F80">
-        <v>50</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="I80" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" t="s">
+      <c r="B81" t="s">
+        <v>13</v>
+      </c>
+      <c r="C81">
+        <v>30.476721000000001</v>
+      </c>
+      <c r="D81">
+        <v>-99.799796999999998</v>
+      </c>
+      <c r="E81">
+        <v>570.4</v>
+      </c>
+      <c r="F81">
+        <v>50</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I81" s="3">
+        <v>45798.444675925923</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" t="s">
+        <v>191</v>
+      </c>
+      <c r="B82" t="s">
+        <v>13</v>
+      </c>
+      <c r="C82">
+        <v>30.47852</v>
+      </c>
+      <c r="D82">
+        <v>-99.781137000000001</v>
+      </c>
+      <c r="E82">
+        <v>515.1</v>
+      </c>
+      <c r="F82">
+        <v>50</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H82" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B81" t="s">
-        <v>10</v>
-      </c>
-      <c r="C81" t="s">
-        <v>256</v>
-      </c>
-      <c r="D81" t="s">
-        <v>256</v>
-      </c>
-      <c r="E81">
-        <v>530</v>
-      </c>
-      <c r="F81">
-        <v>27</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H81" s="2" t="s">
+      <c r="I82" t="s">
         <v>190</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" t="s">
-        <v>192</v>
-      </c>
-      <c r="B82" t="s">
-        <v>10</v>
-      </c>
-      <c r="C82" t="s">
-        <v>256</v>
-      </c>
-      <c r="D82" t="s">
-        <v>256</v>
-      </c>
-      <c r="E82">
-        <v>532.20000000000005</v>
-      </c>
-      <c r="F82">
-        <v>50</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B83" t="s">
-        <v>10</v>
-      </c>
-      <c r="C83" t="s">
-        <v>256</v>
-      </c>
-      <c r="D83" t="s">
-        <v>256</v>
+        <v>13</v>
+      </c>
+      <c r="C83">
+        <v>30.478370000000002</v>
+      </c>
+      <c r="D83">
+        <v>-99.781052000000003</v>
       </c>
       <c r="E83">
-        <v>532.20000000000005</v>
+        <v>515.1</v>
       </c>
       <c r="F83">
         <v>50</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="I83" s="3">
-        <v>45797.598749999997</v>
+        <v>189</v>
+      </c>
+      <c r="I83" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B84" t="s">
-        <v>10</v>
-      </c>
-      <c r="C84" t="s">
-        <v>256</v>
-      </c>
-      <c r="D84" t="s">
-        <v>256</v>
+        <v>13</v>
+      </c>
+      <c r="C84">
+        <v>30.478650999999999</v>
+      </c>
+      <c r="D84">
+        <v>-99.781181000000004</v>
       </c>
       <c r="E84">
-        <v>592.5</v>
+        <v>513.29999999999995</v>
       </c>
       <c r="F84">
         <v>50</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="I84" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
+        <v>197</v>
+      </c>
+      <c r="B85" t="s">
+        <v>13</v>
+      </c>
+      <c r="C85">
+        <v>30.478269000000001</v>
+      </c>
+      <c r="D85">
+        <v>-99.797841000000005</v>
+      </c>
+      <c r="E85">
+        <v>551.4</v>
+      </c>
+      <c r="F85">
+        <v>50</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I85" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B85" t="s">
-        <v>10</v>
-      </c>
-      <c r="C85" t="s">
-        <v>256</v>
-      </c>
-      <c r="D85" t="s">
-        <v>256</v>
-      </c>
-      <c r="E85">
-        <v>588.6</v>
-      </c>
-      <c r="F85">
-        <v>50</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="I85" t="s">
+    </row>
+    <row r="86" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" t="s">
+        <v>194</v>
+      </c>
+      <c r="B86" t="s">
+        <v>13</v>
+      </c>
+      <c r="C86">
+        <v>30.478256999999999</v>
+      </c>
+      <c r="D86">
+        <v>-99.797663999999997</v>
+      </c>
+      <c r="E86">
+        <v>550.5</v>
+      </c>
+      <c r="F86">
+        <v>50</v>
+      </c>
+      <c r="G86" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="86" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" t="s">
+      <c r="H86" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87" t="s">
         <v>199</v>
       </c>
-      <c r="B86" t="s">
-        <v>10</v>
-      </c>
-      <c r="C86" t="s">
-        <v>256</v>
-      </c>
-      <c r="D86" t="s">
-        <v>256</v>
-      </c>
-      <c r="E86">
-        <v>584.9</v>
-      </c>
-      <c r="F86">
-        <v>50</v>
-      </c>
-      <c r="G86" s="2" t="s">
+      <c r="B87" t="s">
+        <v>13</v>
+      </c>
+      <c r="C87">
+        <v>30.478331000000001</v>
+      </c>
+      <c r="D87">
+        <v>-99.798000000000002</v>
+      </c>
+      <c r="E87">
+        <v>547.6</v>
+      </c>
+      <c r="F87">
+        <v>50</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I87" t="s">
         <v>200</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" t="s">
-        <v>201</v>
-      </c>
-      <c r="B87" t="s">
-        <v>10</v>
-      </c>
-      <c r="C87" t="s">
-        <v>256</v>
-      </c>
-      <c r="D87" t="s">
-        <v>256</v>
-      </c>
-      <c r="E87">
-        <v>612</v>
-      </c>
-      <c r="F87">
-        <v>50</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
@@ -3587,126 +3509,129 @@
         <v>203</v>
       </c>
       <c r="B88" t="s">
-        <v>10</v>
-      </c>
-      <c r="C88" t="s">
-        <v>256</v>
-      </c>
-      <c r="D88" t="s">
-        <v>256</v>
+        <v>13</v>
+      </c>
+      <c r="C88">
+        <v>30.474893000000002</v>
+      </c>
+      <c r="D88">
+        <v>-99.779758999999999</v>
       </c>
       <c r="E88">
-        <v>611.1</v>
+        <v>520</v>
       </c>
       <c r="F88">
         <v>50</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>202</v>
       </c>
       <c r="I88" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B89" t="s">
-        <v>10</v>
-      </c>
-      <c r="C89" t="s">
-        <v>256</v>
-      </c>
-      <c r="D89" t="s">
-        <v>256</v>
+        <v>13</v>
+      </c>
+      <c r="C89">
+        <v>30.474945999999999</v>
+      </c>
+      <c r="D89">
+        <v>-99.779919000000007</v>
       </c>
       <c r="E89">
-        <v>609.9</v>
-      </c>
-      <c r="F89">
-        <v>50</v>
+        <v>520</v>
+      </c>
+      <c r="F89" t="s">
+        <v>147</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>200</v>
+        <v>92</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="90" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I89" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
+        <v>204</v>
+      </c>
+      <c r="B90" t="s">
+        <v>13</v>
+      </c>
+      <c r="C90">
+        <v>30.474886000000001</v>
+      </c>
+      <c r="D90">
+        <v>-99.779607999999996</v>
+      </c>
+      <c r="E90">
+        <v>520</v>
+      </c>
+      <c r="F90" t="s">
+        <v>147</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="I90" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91" t="s">
         <v>205</v>
       </c>
-      <c r="B90" t="s">
-        <v>10</v>
-      </c>
-      <c r="C90" t="s">
-        <v>256</v>
-      </c>
-      <c r="D90" t="s">
-        <v>256</v>
-      </c>
-      <c r="E90">
-        <v>523</v>
-      </c>
-      <c r="F90">
-        <v>50</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" t="s">
-        <v>206</v>
-      </c>
       <c r="B91" t="s">
-        <v>10</v>
-      </c>
-      <c r="C91" t="s">
-        <v>256</v>
-      </c>
-      <c r="D91" t="s">
-        <v>256</v>
+        <v>13</v>
+      </c>
+      <c r="C91">
+        <v>30.480160000000001</v>
+      </c>
+      <c r="D91">
+        <v>-99.802869999999999</v>
       </c>
       <c r="E91">
-        <v>540.1</v>
+        <v>606.20000000000005</v>
       </c>
       <c r="F91">
-        <v>332</v>
+        <v>110</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H91" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92" t="s">
         <v>207</v>
       </c>
-      <c r="I91" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" t="s">
-        <v>208</v>
-      </c>
       <c r="B92" t="s">
         <v>10</v>
       </c>
       <c r="C92" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D92" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E92">
-        <v>534.9</v>
+        <v>526.1</v>
       </c>
       <c r="F92">
         <v>10</v>
@@ -3715,656 +3640,149 @@
         <v>11</v>
       </c>
       <c r="H92" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I92" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" t="s">
+        <v>208</v>
+      </c>
+      <c r="B93" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" t="s">
+        <v>220</v>
+      </c>
+      <c r="D93" t="s">
+        <v>220</v>
+      </c>
+      <c r="E93">
+        <v>608.1</v>
+      </c>
+      <c r="F93">
+        <v>110</v>
+      </c>
+      <c r="G93" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="I92" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" t="s">
+      <c r="H93" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B93" t="s">
-        <v>10</v>
-      </c>
-      <c r="C93" t="s">
-        <v>256</v>
-      </c>
-      <c r="D93" t="s">
-        <v>256</v>
-      </c>
-      <c r="E93">
-        <v>522.1</v>
-      </c>
-      <c r="F93">
-        <v>15</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H93" s="2" t="s">
+      <c r="I93" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
         <v>212</v>
       </c>
       <c r="B94" t="s">
-        <v>14</v>
-      </c>
-      <c r="C94">
-        <v>30.481009</v>
-      </c>
-      <c r="D94">
-        <v>-99.803982000000005</v>
+        <v>10</v>
+      </c>
+      <c r="C94" t="s">
+        <v>220</v>
+      </c>
+      <c r="D94" t="s">
+        <v>220</v>
       </c>
       <c r="E94">
-        <v>608.1</v>
+        <v>523</v>
       </c>
       <c r="F94">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>140</v>
+        <v>213</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B95" t="s">
         <v>10</v>
       </c>
       <c r="C95" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D95" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E95">
-        <v>592.5</v>
+        <v>527</v>
       </c>
       <c r="F95">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>215</v>
+      </c>
+      <c r="I95" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B96" t="s">
-        <v>14</v>
-      </c>
-      <c r="C96">
-        <v>30.476970000000001</v>
-      </c>
-      <c r="D96">
-        <v>-99.799980000000005</v>
+        <v>10</v>
+      </c>
+      <c r="C96" t="s">
+        <v>220</v>
+      </c>
+      <c r="D96" t="s">
+        <v>220</v>
       </c>
       <c r="E96">
-        <v>583.70000000000005</v>
+        <v>526.1</v>
       </c>
       <c r="F96">
         <v>50</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>216</v>
+        <v>11</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="I96" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
         <v>218</v>
       </c>
       <c r="B97" t="s">
-        <v>14</v>
-      </c>
-      <c r="C97">
-        <v>30.476849999999999</v>
-      </c>
-      <c r="D97">
-        <v>-99.799880000000002</v>
+        <v>10</v>
+      </c>
+      <c r="C97" t="s">
+        <v>220</v>
+      </c>
+      <c r="D97" t="s">
+        <v>220</v>
       </c>
       <c r="E97">
-        <v>580.29999999999995</v>
+        <v>532.5</v>
       </c>
       <c r="F97">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H97" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="H97" s="2" t="s">
-        <v>217</v>
-      </c>
       <c r="I97" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="115.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A98" t="s">
-        <v>221</v>
-      </c>
-      <c r="B98" t="s">
-        <v>14</v>
-      </c>
-      <c r="C98">
-        <v>30.476721000000001</v>
-      </c>
-      <c r="D98">
-        <v>-99.799796999999998</v>
-      </c>
-      <c r="E98">
-        <v>570.4</v>
-      </c>
-      <c r="F98">
-        <v>50</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="I98" s="3">
-        <v>45798.444675925923</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A99" t="s">
-        <v>222</v>
-      </c>
-      <c r="B99" t="s">
-        <v>14</v>
-      </c>
-      <c r="C99">
-        <v>30.478370000000002</v>
-      </c>
-      <c r="D99">
-        <v>-99.781052000000003</v>
-      </c>
-      <c r="E99">
-        <v>515.1</v>
-      </c>
-      <c r="F99">
-        <v>50</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="I99" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A100" t="s">
-        <v>225</v>
-      </c>
-      <c r="B100" t="s">
-        <v>14</v>
-      </c>
-      <c r="C100">
-        <v>30.47852</v>
-      </c>
-      <c r="D100">
-        <v>-99.781137000000001</v>
-      </c>
-      <c r="E100">
-        <v>515.1</v>
-      </c>
-      <c r="F100">
-        <v>50</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="I100" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A101" t="s">
-        <v>226</v>
-      </c>
-      <c r="B101" t="s">
-        <v>14</v>
-      </c>
-      <c r="C101">
-        <v>30.478650999999999</v>
-      </c>
-      <c r="D101">
-        <v>-99.781181000000004</v>
-      </c>
-      <c r="E101">
-        <v>513.29999999999995</v>
-      </c>
-      <c r="F101">
-        <v>50</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="I101" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A102" t="s">
-        <v>228</v>
-      </c>
-      <c r="B102" t="s">
-        <v>14</v>
-      </c>
-      <c r="C102">
-        <v>30.478256999999999</v>
-      </c>
-      <c r="D102">
-        <v>-99.797663999999997</v>
-      </c>
-      <c r="E102">
-        <v>550.5</v>
-      </c>
-      <c r="F102">
-        <v>50</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A103" t="s">
-        <v>231</v>
-      </c>
-      <c r="B103" t="s">
-        <v>14</v>
-      </c>
-      <c r="C103">
-        <v>30.478269000000001</v>
-      </c>
-      <c r="D103">
-        <v>-99.797841000000005</v>
-      </c>
-      <c r="E103">
-        <v>551.4</v>
-      </c>
-      <c r="F103">
-        <v>50</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="I103" s="3" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A104" t="s">
-        <v>233</v>
-      </c>
-      <c r="B104" t="s">
-        <v>14</v>
-      </c>
-      <c r="C104">
-        <v>30.478331000000001</v>
-      </c>
-      <c r="D104">
-        <v>-99.798000000000002</v>
-      </c>
-      <c r="E104">
-        <v>547.6</v>
-      </c>
-      <c r="F104">
-        <v>50</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H104" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="I104" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A105" t="s">
-        <v>235</v>
-      </c>
-      <c r="B105" t="s">
-        <v>14</v>
-      </c>
-      <c r="C105">
-        <v>30.474945999999999</v>
-      </c>
-      <c r="D105">
-        <v>-99.779919000000007</v>
-      </c>
-      <c r="E105">
-        <v>520</v>
-      </c>
-      <c r="F105" t="s">
-        <v>181</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H105" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="I105" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A106" t="s">
-        <v>237</v>
-      </c>
-      <c r="B106" t="s">
-        <v>14</v>
-      </c>
-      <c r="C106">
-        <v>30.474893000000002</v>
-      </c>
-      <c r="D106">
-        <v>-99.779758999999999</v>
-      </c>
-      <c r="E106">
-        <v>520</v>
-      </c>
-      <c r="F106">
-        <v>50</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="I106" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A107" t="s">
-        <v>238</v>
-      </c>
-      <c r="B107" t="s">
-        <v>14</v>
-      </c>
-      <c r="C107">
-        <v>30.474886000000001</v>
-      </c>
-      <c r="D107">
-        <v>-99.779607999999996</v>
-      </c>
-      <c r="E107">
-        <v>520</v>
-      </c>
-      <c r="F107" t="s">
-        <v>181</v>
-      </c>
-      <c r="G107" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="I107" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A108" t="s">
-        <v>239</v>
-      </c>
-      <c r="B108" t="s">
-        <v>14</v>
-      </c>
-      <c r="C108">
-        <v>30.480160000000001</v>
-      </c>
-      <c r="D108">
-        <v>-99.802869999999999</v>
-      </c>
-      <c r="E108">
-        <v>606.20000000000005</v>
-      </c>
-      <c r="F108">
-        <v>110</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A109" t="s">
-        <v>241</v>
-      </c>
-      <c r="B109" t="s">
-        <v>10</v>
-      </c>
-      <c r="C109" t="s">
-        <v>256</v>
-      </c>
-      <c r="D109" t="s">
-        <v>256</v>
-      </c>
-      <c r="E109">
-        <v>598</v>
-      </c>
-      <c r="F109">
-        <v>10</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A110" t="s">
-        <v>243</v>
-      </c>
-      <c r="B110" t="s">
-        <v>10</v>
-      </c>
-      <c r="C110" t="s">
-        <v>256</v>
-      </c>
-      <c r="D110" t="s">
-        <v>256</v>
-      </c>
-      <c r="E110">
-        <v>526.1</v>
-      </c>
-      <c r="F110">
-        <v>10</v>
-      </c>
-      <c r="G110" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H110" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I110" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A111" t="s">
-        <v>244</v>
-      </c>
-      <c r="B111" t="s">
-        <v>10</v>
-      </c>
-      <c r="C111" t="s">
-        <v>256</v>
-      </c>
-      <c r="D111" t="s">
-        <v>256</v>
-      </c>
-      <c r="E111">
-        <v>608.1</v>
-      </c>
-      <c r="F111">
-        <v>110</v>
-      </c>
-      <c r="G111" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="I111" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A112" t="s">
-        <v>248</v>
-      </c>
-      <c r="B112" t="s">
-        <v>10</v>
-      </c>
-      <c r="C112" t="s">
-        <v>256</v>
-      </c>
-      <c r="D112" t="s">
-        <v>256</v>
-      </c>
-      <c r="E112">
-        <v>523</v>
-      </c>
-      <c r="F112">
-        <v>15</v>
-      </c>
-      <c r="G112" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A113" t="s">
-        <v>250</v>
-      </c>
-      <c r="B113" t="s">
-        <v>10</v>
-      </c>
-      <c r="C113" t="s">
-        <v>256</v>
-      </c>
-      <c r="D113" t="s">
-        <v>256</v>
-      </c>
-      <c r="E113">
-        <v>527</v>
-      </c>
-      <c r="F113">
-        <v>50</v>
-      </c>
-      <c r="G113" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="I113" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A114" t="s">
-        <v>252</v>
-      </c>
-      <c r="B114" t="s">
-        <v>10</v>
-      </c>
-      <c r="C114" t="s">
-        <v>256</v>
-      </c>
-      <c r="D114" t="s">
-        <v>256</v>
-      </c>
-      <c r="E114">
-        <v>526.1</v>
-      </c>
-      <c r="F114">
-        <v>50</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A115" t="s">
-        <v>254</v>
-      </c>
-      <c r="B115" t="s">
-        <v>10</v>
-      </c>
-      <c r="C115" t="s">
-        <v>256</v>
-      </c>
-      <c r="D115" t="s">
-        <v>256</v>
-      </c>
-      <c r="E115">
-        <v>532.5</v>
-      </c>
-      <c r="F115">
-        <v>10</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="I115" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
